--- a/outputs/daily/hr_rankings_2026-08-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-10.xlsx
@@ -35411,27 +35411,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>681146</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Jonah Bride</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -35441,22 +35441,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -35474,26 +35474,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>17.5</v>
+        <v>25.5</v>
       </c>
       <c r="Q116" t="n">
-        <v>32.4</v>
+        <v>42.1</v>
       </c>
       <c r="R116" t="n">
-        <v>47.1</v>
+        <v>58.7</v>
       </c>
       <c r="S116" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T116" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U116" t="n">
-        <v>16.6</v>
+        <v>19.5</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -35544,17 +35544,17 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -35564,117 +35564,117 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 1 games: 1/4, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>93.25</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>98.1432</t>
+          <t>97.149</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>0.2346</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1049</t>
+          <t>0.1041</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.2994</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>71.46</t>
+          <t>66.22</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>40.28</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.0869</t>
+          <t>0.0054</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3436</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr">
         <is>
-          <t>214 deg</t>
+          <t>242 deg</t>
         </is>
       </c>
       <c r="BH116" t="inlineStr">
@@ -35684,27 +35684,27 @@
       </c>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=32.7073&amp;lon=-117.1573</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BK116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL116" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM116" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BN116" t="inlineStr"/>
@@ -35715,27 +35715,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>543760</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -35745,17 +35745,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -35764,7 +35764,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -35778,26 +35778,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>26.6</v>
+        <v>17.5</v>
       </c>
       <c r="Q117" t="n">
-        <v>40.9</v>
+        <v>32.4</v>
       </c>
       <c r="R117" t="n">
-        <v>50.4</v>
+        <v>47.1</v>
       </c>
       <c r="S117" t="n">
-        <v>59.8</v>
+        <v>95.5</v>
       </c>
       <c r="T117" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U117" t="n">
-        <v>56.2</v>
+        <v>16.6</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -35858,22 +35858,22 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -35883,102 +35883,102 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>97.7128</t>
+          <t>98.1432</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.3978</t>
+          <t>0.332</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1049</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.2994</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>71.46</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>22.51</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1445</t>
+          <t>0.0869</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.4067</t>
+          <t>0.3436</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr">
         <is>
-          <t>344 deg</t>
+          <t>214 deg</t>
         </is>
       </c>
       <c r="BH117" t="inlineStr">
@@ -35988,27 +35988,27 @@
       </c>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=32.7073&amp;lon=-117.1573</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BK117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BL117" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BM117" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BN117" t="inlineStr"/>
@@ -36019,27 +36019,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>703607</t>
+          <t>543760</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -36049,17 +36049,17 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -36068,7 +36068,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -36086,22 +36086,22 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>37.2</v>
+        <v>26.6</v>
       </c>
       <c r="Q118" t="n">
-        <v>33.1</v>
+        <v>40.9</v>
       </c>
       <c r="R118" t="n">
-        <v>62.9</v>
+        <v>50.4</v>
       </c>
       <c r="S118" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T118" t="n">
         <v>50</v>
       </c>
       <c r="U118" t="n">
-        <v>37.8</v>
+        <v>56.2</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -36140,7 +36140,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr"/>
@@ -36157,27 +36157,27 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -36187,102 +36187,102 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>87.11</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>104.2571</t>
+          <t>97.7128</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.3978</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>31.93</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1445</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.4067</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>344 deg</t>
         </is>
       </c>
       <c r="BH118" t="inlineStr">
@@ -36292,27 +36292,27 @@
       </c>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BK118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL118" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BM118" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BN118" t="inlineStr"/>
@@ -36323,27 +36323,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>808982</t>
+          <t>703607</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -36353,17 +36353,17 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -36372,7 +36372,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -36386,26 +36386,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>10.8</v>
+        <v>37.2</v>
       </c>
       <c r="Q119" t="n">
-        <v>29.4</v>
+        <v>33.1</v>
       </c>
       <c r="R119" t="n">
-        <v>45.3</v>
+        <v>62.9</v>
       </c>
       <c r="S119" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U119" t="n">
-        <v>63.1</v>
+        <v>37.8</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -36444,7 +36444,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -36461,27 +36461,27 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -36491,102 +36491,102 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>96.629</t>
+          <t>104.2571</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.0947</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH119" t="inlineStr">
@@ -36596,27 +36596,27 @@
       </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL119" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM119" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN119" t="inlineStr"/>
@@ -36627,27 +36627,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>643446</t>
+          <t>808982</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -36657,17 +36657,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -36676,7 +36676,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -36690,26 +36690,26 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q120" t="n">
-        <v>33.1</v>
+        <v>29.4</v>
       </c>
       <c r="R120" t="n">
-        <v>62.9</v>
+        <v>45.3</v>
       </c>
       <c r="S120" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T120" t="n">
         <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>24.9</v>
+        <v>63.1</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -36765,27 +36765,27 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -36795,102 +36795,102 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>96.5924</t>
+          <t>96.629</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3649</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.0964</t>
+          <t>0.0947</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.3104</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>69.09</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.4346</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>18.23</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BH120" t="inlineStr">
@@ -36900,27 +36900,27 @@
       </c>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BK120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BL120" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BM120" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BN120" t="inlineStr"/>
@@ -36931,22 +36931,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>643446</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -36961,17 +36961,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -36980,7 +36980,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>40.7</v>
+        <v>41.1</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -36994,26 +36994,26 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>23.3</v>
+        <v>11.5</v>
       </c>
       <c r="Q121" t="n">
-        <v>35.7</v>
+        <v>33.1</v>
       </c>
       <c r="R121" t="n">
-        <v>58.2</v>
+        <v>62.9</v>
       </c>
       <c r="S121" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T121" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U121" t="n">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -37069,12 +37069,12 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -37084,12 +37084,12 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -37099,102 +37099,102 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>99.5961</t>
+          <t>96.5924</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.3649</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.1152</t>
+          <t>0.0964</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.3104</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1224</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr">
         <is>
-          <t>280 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH121" t="inlineStr">
@@ -37204,12 +37204,12 @@
       </c>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK121" t="inlineStr">
@@ -37219,12 +37219,12 @@
       </c>
       <c r="BL121" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM121" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN121" t="inlineStr"/>
@@ -37235,27 +37235,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>664770</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-10T23:07:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -37265,17 +37265,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -37284,7 +37284,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>40.4</v>
+        <v>40.7</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -37298,26 +37298,26 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>9.300000000000001</v>
+        <v>23.3</v>
       </c>
       <c r="Q122" t="n">
-        <v>36.2</v>
+        <v>35.7</v>
       </c>
       <c r="R122" t="n">
-        <v>48.9</v>
+        <v>58.2</v>
       </c>
       <c r="S122" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T122" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U122" t="n">
-        <v>34.2</v>
+        <v>24</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -37378,22 +37378,22 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 15.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -37403,102 +37403,102 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>86.99</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>96.7915</t>
+          <t>99.5961</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3479</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1152</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1224</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD122" t="inlineStr">
         <is>
-          <t>0.3859</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
-          <t>0.1369</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG122" t="inlineStr">
         <is>
-          <t>169 deg</t>
+          <t>280 deg</t>
         </is>
       </c>
       <c r="BH122" t="inlineStr">
@@ -37508,12 +37508,12 @@
       </c>
       <c r="BI122" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=43.6414&amp;lon=-79.3894</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
         </is>
       </c>
       <c r="BJ122" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>19</t>
         </is>
       </c>
       <c r="BK122" t="inlineStr">
@@ -37523,12 +37523,12 @@
       </c>
       <c r="BL122" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>110</t>
         </is>
       </c>
       <c r="BM122" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BN122" t="inlineStr"/>
@@ -37539,24 +37539,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>657136</t>
+          <t>664770</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>2026-08-10T23:07:00Z</t>
@@ -37569,17 +37569,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>592791</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -37588,7 +37588,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -37602,26 +37602,26 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>15.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q123" t="n">
-        <v>69.09999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="R123" t="n">
         <v>48.9</v>
       </c>
       <c r="S123" t="n">
-        <v>40.2</v>
+        <v>88.7</v>
       </c>
       <c r="T123" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U123" t="n">
-        <v>18.3</v>
+        <v>34.2</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -37677,12 +37677,12 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -37692,112 +37692,112 @@
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 1 HR</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 25.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>86.27</t>
+          <t>86.99</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>99.0481</t>
+          <t>96.7915</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3479</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>0.1027</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>0.2877</t>
+          <t>0.294</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>34.01</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>0.1005</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="BD123" t="inlineStr">
         <is>
-          <t>0.5073</t>
+          <t>0.3859</t>
         </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
-          <t>0.2502</t>
+          <t>0.1369</t>
         </is>
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr">
@@ -37843,27 +37843,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>657136</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-10T23:07:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -37873,17 +37873,17 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Jameson Taillon</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>690928</t>
+          <t>592791</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -37906,26 +37906,26 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>7.4</v>
+        <v>15.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>33.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="R124" t="n">
-        <v>55.1</v>
+        <v>48.9</v>
       </c>
       <c r="S124" t="n">
-        <v>90.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T124" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U124" t="n">
-        <v>33.1</v>
+        <v>18.3</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -37981,12 +37981,12 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -37996,117 +37996,117 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/32, 1 HR</t>
+          <t>Last 7 games: 2/20, 1 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 25.4 HR allowed</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>86.27</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>93.9815</t>
+          <t>99.0481</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.3693</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.0851</t>
+          <t>0.1027</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>62.99</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>39.89</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.1147</t>
+          <t>0.1005</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>0.3821</t>
+          <t>0.5073</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.2502</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
         <is>
-          <t>188 deg</t>
+          <t>169 deg</t>
         </is>
       </c>
       <c r="BH124" t="inlineStr">
@@ -38116,12 +38116,12 @@
       </c>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=43.6414&amp;lon=-79.3894</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BK124" t="inlineStr">
@@ -38131,12 +38131,12 @@
       </c>
       <c r="BL124" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BM124" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BN124" t="inlineStr"/>
@@ -38147,27 +38147,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -38177,17 +38177,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>690928</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -38196,7 +38196,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>39.4</v>
+        <v>40.2</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -38210,26 +38210,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>42.2</v>
+        <v>7.4</v>
       </c>
       <c r="Q125" t="n">
-        <v>18.6</v>
+        <v>33.1</v>
       </c>
       <c r="R125" t="n">
-        <v>45.3</v>
+        <v>55.1</v>
       </c>
       <c r="S125" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T125" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U125" t="n">
-        <v>81.7</v>
+        <v>33.1</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -38285,27 +38285,27 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/32, 1 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -38315,102 +38315,102 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>93.9815</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3693</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.0851</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>62.99</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1147</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.3709</t>
+          <t>0.3821</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>188 deg</t>
         </is>
       </c>
       <c r="BH125" t="inlineStr">
@@ -38420,27 +38420,27 @@
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BK125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL125" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM125" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BN125" t="inlineStr"/>
@@ -38451,27 +38451,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>665966</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Carlos Narvaez</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -38486,12 +38486,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -38500,7 +38500,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -38514,17 +38514,17 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>33.3</v>
+        <v>42.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>43.4</v>
+        <v>18.6</v>
       </c>
       <c r="R126" t="n">
-        <v>51.6</v>
+        <v>45.3</v>
       </c>
       <c r="S126" t="n">
         <v>40.2</v>
@@ -38533,7 +38533,7 @@
         <v>50</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -38589,132 +38589,132 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>91.24</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>100.2964</t>
+          <t>101.5346</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.418</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.1382</t>
+          <t>0.1753</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>0.3215</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>68.11</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.1542</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.4431</t>
+          <t>0.3709</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.1974</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr">
         <is>
-          <t>24 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BH126" t="inlineStr">
@@ -38724,27 +38724,27 @@
       </c>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="BK126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL126" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="BK126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL126" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="BM126" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BN126" t="inlineStr"/>
@@ -38755,27 +38755,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>665966</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Carlos Narvaez</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -38790,12 +38790,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>28.3</v>
+        <v>33.3</v>
       </c>
       <c r="Q127" t="n">
-        <v>35.7</v>
+        <v>43.4</v>
       </c>
       <c r="R127" t="n">
-        <v>58.2</v>
+        <v>51.6</v>
       </c>
       <c r="S127" t="n">
         <v>40.2</v>
@@ -38837,7 +38837,7 @@
         <v>50</v>
       </c>
       <c r="U127" t="n">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -38893,67 +38893,67 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.24</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>98.9141</t>
+          <t>100.2964</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1382</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.2854</t>
+          <t>0.279</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
@@ -38963,62 +38963,62 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.4431</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1974</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
         <is>
-          <t>280 deg</t>
+          <t>24 deg</t>
         </is>
       </c>
       <c r="BH127" t="inlineStr">
@@ -39028,27 +39028,27 @@
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BK127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BL127" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM127" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BN127" t="inlineStr"/>
@@ -39059,27 +39059,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -39089,17 +39089,17 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -39122,26 +39122,26 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>31</v>
+        <v>28.3</v>
       </c>
       <c r="Q128" t="n">
-        <v>18.6</v>
+        <v>35.7</v>
       </c>
       <c r="R128" t="n">
-        <v>45.3</v>
+        <v>58.2</v>
       </c>
       <c r="S128" t="n">
-        <v>88.7</v>
+        <v>40.2</v>
       </c>
       <c r="T128" t="n">
         <v>50</v>
       </c>
       <c r="U128" t="n">
-        <v>18.3</v>
+        <v>50.3</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -39197,12 +39197,12 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
@@ -39212,12 +39212,12 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -39227,102 +39227,102 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>100.0961</t>
+          <t>98.9141</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4369</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1508</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3445</t>
+          <t>0.2854</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>29.43</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1849</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>0.3709</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>280 deg</t>
         </is>
       </c>
       <c r="BH128" t="inlineStr">
@@ -39332,27 +39332,27 @@
       </c>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>19</t>
         </is>
       </c>
       <c r="BK128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL128" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>110</t>
         </is>
       </c>
       <c r="BM128" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BN128" t="inlineStr"/>
@@ -39363,27 +39363,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>668885</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Jeremy Pena</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -39398,21 +39398,21 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -39426,26 +39426,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>10.5</v>
+        <v>31</v>
       </c>
       <c r="Q129" t="n">
-        <v>35.6</v>
+        <v>18.6</v>
       </c>
       <c r="R129" t="n">
-        <v>51.6</v>
+        <v>45.3</v>
       </c>
       <c r="S129" t="n">
         <v>88.7</v>
       </c>
       <c r="T129" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -39501,27 +39501,27 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -39531,102 +39531,102 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>86.69</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>97.1877</t>
+          <t>100.0961</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.3421</t>
+          <t>0.4369</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.0918</t>
+          <t>0.1508</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.3198</t>
+          <t>0.3445</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>68.83</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.0788</t>
+          <t>0.1849</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3709</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
         <is>
-          <t>24 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BH129" t="inlineStr">
@@ -39636,27 +39636,27 @@
       </c>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="BK129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL129" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="BK129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL129" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="BM129" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BN129" t="inlineStr"/>
@@ -39667,27 +39667,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>668885</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -39697,26 +39697,26 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -39730,26 +39730,26 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q130" t="n">
-        <v>43.2</v>
+        <v>35.6</v>
       </c>
       <c r="R130" t="n">
-        <v>55.1</v>
+        <v>51.6</v>
       </c>
       <c r="S130" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T130" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U130" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -39788,7 +39788,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr"/>
@@ -39805,12 +39805,12 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -39820,12 +39820,12 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -39835,102 +39835,102 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>86.69</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>98.6827</t>
+          <t>97.1877</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.3386</t>
+          <t>0.3421</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.0888</t>
+          <t>0.0918</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.3198</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>68.83</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.0897</t>
+          <t>0.0788</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
         <is>
-          <t>188 deg</t>
+          <t>24 deg</t>
         </is>
       </c>
       <c r="BH130" t="inlineStr">
@@ -39940,27 +39940,27 @@
       </c>
       <c r="BI130" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BJ130" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BK130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BL130" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM130" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BN130" t="inlineStr"/>
@@ -39971,27 +39971,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -40006,21 +40006,21 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>38.7</v>
+        <v>39</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -40034,26 +40034,26 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>13.3</v>
+        <v>15.5</v>
       </c>
       <c r="Q131" t="n">
-        <v>21.5</v>
+        <v>43.2</v>
       </c>
       <c r="R131" t="n">
-        <v>62.9</v>
+        <v>55.1</v>
       </c>
       <c r="S131" t="n">
         <v>71.7</v>
       </c>
       <c r="T131" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U131" t="n">
-        <v>52.8</v>
+        <v>14.6</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr"/>
@@ -40114,127 +40114,127 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 13.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>97.3793</t>
+          <t>98.6827</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.3521</t>
+          <t>0.3386</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.0888</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.2761</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1629</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>85.92</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.1261</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>188 deg</t>
         </is>
       </c>
       <c r="BH131" t="inlineStr">
@@ -40244,12 +40244,12 @@
       </c>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BK131" t="inlineStr">
@@ -40259,12 +40259,12 @@
       </c>
       <c r="BL131" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM131" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BN131" t="inlineStr"/>
@@ -40275,27 +40275,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-11T02:10:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -40305,17 +40305,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -40324,7 +40324,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -40342,22 +40342,22 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>23.8</v>
+        <v>13.3</v>
       </c>
       <c r="Q132" t="n">
-        <v>26.8</v>
+        <v>21.5</v>
       </c>
       <c r="R132" t="n">
-        <v>56.6</v>
+        <v>62.9</v>
       </c>
       <c r="S132" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T132" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U132" t="n">
-        <v>12</v>
+        <v>52.8</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -40418,157 +40418,157 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Hot streak: 2 HR in last 7 games</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 13.6 HR allowed</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+        </is>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>30.96</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>85.32</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>97.3793</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>0.3521</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
+          <t>0.2761</t>
+        </is>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>72.89</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>30.55</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>46.44</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>22.34</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>0.1629</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>31.66</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>85.92</t>
+        </is>
+      </c>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>0.3368</t>
+        </is>
+      </c>
+      <c r="BE132" t="inlineStr">
+        <is>
+          <t>0.1261</t>
+        </is>
+      </c>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>32.41</t>
+        </is>
+      </c>
+      <c r="BG132" t="inlineStr">
+        <is>
+          <t>225 deg</t>
+        </is>
+      </c>
+      <c r="BH132" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BI132" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+        </is>
+      </c>
+      <c r="BJ132" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BK132" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AL132" t="inlineStr">
-        <is>
-          <t>switch hitter; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>5.32</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>40.16</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>88.59</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>100.0202</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>0.3401</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>0.1018</t>
-        </is>
-      </c>
-      <c r="AT132" t="inlineStr">
-        <is>
-          <t>0.3108</t>
-        </is>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>73.33</t>
-        </is>
-      </c>
-      <c r="AV132" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
-      </c>
-      <c r="AW132" t="inlineStr">
-        <is>
-          <t>40.54</t>
-        </is>
-      </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>0.134</t>
-        </is>
-      </c>
-      <c r="BA132" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB132" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="BC132" t="inlineStr">
-        <is>
-          <t>86.66</t>
-        </is>
-      </c>
-      <c r="BD132" t="inlineStr">
-        <is>
-          <t>0.3468</t>
-        </is>
-      </c>
-      <c r="BE132" t="inlineStr">
-        <is>
-          <t>0.1268</t>
-        </is>
-      </c>
-      <c r="BF132" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="BG132" t="inlineStr">
-        <is>
-          <t>249 deg</t>
-        </is>
-      </c>
-      <c r="BH132" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BI132" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BJ132" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="BK132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BL132" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM132" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN132" t="inlineStr"/>
@@ -40579,27 +40579,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T02:10:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -40609,26 +40609,26 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Christian Scott</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>681035</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -40646,22 +40646,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>16.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q133" t="n">
-        <v>23.9</v>
+        <v>26.8</v>
       </c>
       <c r="R133" t="n">
-        <v>50.4</v>
+        <v>56.6</v>
       </c>
       <c r="S133" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T133" t="n">
         <v>75</v>
       </c>
       <c r="U133" t="n">
-        <v>27.6</v>
+        <v>12</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -40700,7 +40700,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr"/>
@@ -40717,27 +40717,27 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -40747,102 +40747,102 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>87.01</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>96.7422</t>
+          <t>100.0202</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.3401</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.1251</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.2878</t>
+          <t>0.3108</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>46.42</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.1586</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3468</t>
         </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr">
         <is>
-          <t>344 deg</t>
+          <t>249 deg</t>
         </is>
       </c>
       <c r="BH133" t="inlineStr">
@@ -40852,27 +40852,27 @@
       </c>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>36</t>
         </is>
       </c>
       <c r="BK133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL133" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM133" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BN133" t="inlineStr"/>
@@ -40883,27 +40883,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -40913,22 +40913,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Christian Scott</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>681035</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -40950,22 +40950,22 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>11</v>
+        <v>16.7</v>
       </c>
       <c r="Q134" t="n">
-        <v>35.6</v>
+        <v>23.9</v>
       </c>
       <c r="R134" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="S134" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T134" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U134" t="n">
-        <v>63.1</v>
+        <v>27.6</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -41004,7 +41004,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr"/>
@@ -41021,27 +41021,27 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -41051,102 +41051,102 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>96.5933</t>
+          <t>96.7422</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.3549</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.1251</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.3107</t>
+          <t>0.2878</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>46.42</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.1108</t>
+          <t>0.1586</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr">
         <is>
-          <t>24 deg</t>
+          <t>344 deg</t>
         </is>
       </c>
       <c r="BH134" t="inlineStr">
@@ -41156,27 +41156,27 @@
       </c>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BK134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL134" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BM134" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BN134" t="inlineStr"/>
@@ -41187,27 +41187,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -41222,21 +41222,21 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -41254,22 +41254,22 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="Q135" t="n">
-        <v>33.1</v>
+        <v>35.6</v>
       </c>
       <c r="R135" t="n">
-        <v>62.9</v>
+        <v>51.6</v>
       </c>
       <c r="S135" t="n">
         <v>59.8</v>
       </c>
       <c r="T135" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U135" t="n">
-        <v>12</v>
+        <v>63.1</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -41325,27 +41325,27 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -41355,102 +41355,102 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>85.08</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>97.8166</t>
+          <t>96.5933</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.3576</t>
+          <t>0.3549</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.0977</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.2992</t>
+          <t>0.3107</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1108</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>24 deg</t>
         </is>
       </c>
       <c r="BH135" t="inlineStr">
@@ -41460,27 +41460,27 @@
       </c>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BK135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BL135" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM135" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BN135" t="inlineStr"/>
@@ -41491,27 +41491,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>593871</t>
+          <t>622268</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -41521,17 +41521,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -41540,7 +41540,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -41558,22 +41558,22 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>21.1</v>
+        <v>14.3</v>
       </c>
       <c r="Q136" t="n">
-        <v>38.9</v>
+        <v>33.1</v>
       </c>
       <c r="R136" t="n">
-        <v>50.4</v>
+        <v>62.9</v>
       </c>
       <c r="S136" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T136" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U136" t="n">
-        <v>18.3</v>
+        <v>12</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -41634,22 +41634,22 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 2/10, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -41659,102 +41659,102 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>98.3169</t>
+          <t>97.8166</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3366</t>
+          <t>0.3576</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1301</t>
+          <t>0.0977</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.2639</t>
+          <t>0.2992</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.4067</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>344 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
@@ -41764,27 +41764,27 @@
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL136" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM136" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN136" t="inlineStr"/>
@@ -41795,27 +41795,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>593871</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -41825,17 +41825,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -41858,26 +41858,26 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>21.7</v>
+        <v>21.1</v>
       </c>
       <c r="Q137" t="n">
-        <v>32.4</v>
+        <v>38.9</v>
       </c>
       <c r="R137" t="n">
-        <v>47.1</v>
+        <v>50.4</v>
       </c>
       <c r="S137" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T137" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U137" t="n">
-        <v>32</v>
+        <v>18.3</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -41933,7 +41933,7 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
@@ -41943,17 +41943,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
@@ -41963,102 +41963,102 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>99.068</t>
+          <t>98.3169</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3366</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>0.1301</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.2976</t>
+          <t>0.2639</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.1274</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.3436</t>
+          <t>0.4067</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr">
         <is>
-          <t>214 deg</t>
+          <t>344 deg</t>
         </is>
       </c>
       <c r="BH137" t="inlineStr">
@@ -42068,27 +42068,27 @@
       </c>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=32.7073&amp;lon=-117.1573</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BK137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL137" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BM137" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BN137" t="inlineStr"/>
@@ -42099,27 +42099,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>664761</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -42129,17 +42129,17 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>690928</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -42148,7 +42148,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -42166,22 +42166,22 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>29.2</v>
+        <v>21.7</v>
       </c>
       <c r="Q138" t="n">
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
       <c r="R138" t="n">
-        <v>55.1</v>
+        <v>47.1</v>
       </c>
       <c r="S138" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T138" t="n">
         <v>50</v>
       </c>
       <c r="U138" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -42237,7 +42237,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
@@ -42252,12 +42252,12 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
@@ -42267,102 +42267,102 @@
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>40.29</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>100.1407</t>
+          <t>99.068</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>0.3899</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1057</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>0.3114</t>
+          <t>0.2976</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1274</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="BD138" t="inlineStr">
         <is>
-          <t>0.3821</t>
+          <t>0.3436</t>
         </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BG138" t="inlineStr">
         <is>
-          <t>188 deg</t>
+          <t>214 deg</t>
         </is>
       </c>
       <c r="BH138" t="inlineStr">
@@ -42372,27 +42372,27 @@
       </c>
       <c r="BI138" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=32.7073&amp;lon=-117.1573</t>
         </is>
       </c>
       <c r="BJ138" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BK138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BL138" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BM138" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BN138" t="inlineStr"/>
@@ -42403,27 +42403,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>664761</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-11T02:10:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -42433,26 +42433,26 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>690928</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
@@ -42466,26 +42466,26 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P139" t="n">
-        <v>16.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q139" t="n">
-        <v>28.2</v>
+        <v>33.1</v>
       </c>
       <c r="R139" t="n">
-        <v>56.6</v>
+        <v>55.1</v>
       </c>
       <c r="S139" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T139" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -42541,12 +42541,12 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
@@ -42556,12 +42556,12 @@
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
@@ -42571,102 +42571,102 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>96.8364</t>
+          <t>100.1407</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>0.3506</t>
+          <t>0.3899</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>0.1158</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>0.2982</t>
+          <t>0.3114</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD139" t="inlineStr">
         <is>
-          <t>0.3468</t>
+          <t>0.3821</t>
         </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BG139" t="inlineStr">
         <is>
-          <t>249 deg</t>
+          <t>188 deg</t>
         </is>
       </c>
       <c r="BH139" t="inlineStr">
@@ -42676,12 +42676,12 @@
       </c>
       <c r="BI139" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BJ139" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BK139" t="inlineStr">
@@ -42691,12 +42691,12 @@
       </c>
       <c r="BL139" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM139" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BN139" t="inlineStr"/>
@@ -42707,27 +42707,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>687597</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jordan Beck</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T02:10:00Z</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -42737,26 +42737,26 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>37.2</v>
+        <v>37.7</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -42770,26 +42770,26 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>21.4</v>
+        <v>16.3</v>
       </c>
       <c r="Q140" t="n">
-        <v>35.7</v>
+        <v>28.2</v>
       </c>
       <c r="R140" t="n">
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
       <c r="S140" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T140" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U140" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
@@ -42845,12 +42845,12 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -42860,12 +42860,12 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
@@ -42875,102 +42875,102 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>98.2982</t>
+          <t>96.8364</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.3506</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>0.1171</t>
+          <t>0.1158</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>0.2667</t>
+          <t>0.2982</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>0.1433</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="BD140" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.3468</t>
         </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BG140" t="inlineStr">
         <is>
-          <t>280 deg</t>
+          <t>249 deg</t>
         </is>
       </c>
       <c r="BH140" t="inlineStr">
@@ -42980,12 +42980,12 @@
       </c>
       <c r="BI140" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BJ140" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>36</t>
         </is>
       </c>
       <c r="BK140" t="inlineStr">
@@ -42995,12 +42995,12 @@
       </c>
       <c r="BL140" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM140" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BN140" t="inlineStr"/>
@@ -43011,27 +43011,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>687597</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Jordan Beck</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -43046,21 +43046,21 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -43074,26 +43074,26 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P141" t="n">
-        <v>18.6</v>
+        <v>21.4</v>
       </c>
       <c r="Q141" t="n">
-        <v>34.6</v>
+        <v>35.7</v>
       </c>
       <c r="R141" t="n">
-        <v>51.6</v>
+        <v>58.2</v>
       </c>
       <c r="S141" t="n">
         <v>47.9</v>
       </c>
       <c r="T141" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U141" t="n">
-        <v>28.1</v>
+        <v>32</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -43149,27 +43149,27 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
@@ -43179,102 +43179,102 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>97.4679</t>
+          <t>98.2982</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>0.3404</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.1171</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2667</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>27.97</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1433</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr">
         <is>
-          <t>24 deg</t>
+          <t>280 deg</t>
         </is>
       </c>
       <c r="BH141" t="inlineStr">
@@ -43284,27 +43284,27 @@
       </c>
       <c r="BI141" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
         </is>
       </c>
       <c r="BJ141" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>19</t>
         </is>
       </c>
       <c r="BK141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL141" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>110</t>
         </is>
       </c>
       <c r="BM141" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BN141" t="inlineStr"/>
@@ -43315,27 +43315,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>805779</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jacob Wilson</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -43345,22 +43345,22 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -43378,26 +43378,26 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3</v>
+        <v>18.6</v>
       </c>
       <c r="Q142" t="n">
-        <v>33.1</v>
+        <v>34.6</v>
       </c>
       <c r="R142" t="n">
-        <v>62.9</v>
+        <v>51.6</v>
       </c>
       <c r="S142" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T142" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U142" t="n">
-        <v>14.1</v>
+        <v>28.1</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -43453,27 +43453,27 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -43483,102 +43483,102 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>84.25</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>95.5238</t>
+          <t>97.4679</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.3549</t>
+          <t>0.3404</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.0849</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>24 deg</t>
         </is>
       </c>
       <c r="BH142" t="inlineStr">
@@ -43588,27 +43588,27 @@
       </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BK142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BL142" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM142" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BN142" t="inlineStr"/>
@@ -43619,27 +43619,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>805779</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -43649,26 +43649,26 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -43682,26 +43682,26 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>12.1</v>
+        <v>3</v>
       </c>
       <c r="Q143" t="n">
-        <v>47</v>
+        <v>33.1</v>
       </c>
       <c r="R143" t="n">
-        <v>58.7</v>
+        <v>62.9</v>
       </c>
       <c r="S143" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T143" t="n">
         <v>50</v>
       </c>
       <c r="U143" t="n">
-        <v>54.3</v>
+        <v>14.1</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -43740,7 +43740,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr"/>
@@ -43757,27 +43757,27 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 17.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -43787,102 +43787,102 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.25</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>96.3933</t>
+          <t>95.5238</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.3549</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.0849</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.2914</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>64.36</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>42.91</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.3898</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1537</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr">
         <is>
-          <t>242 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH143" t="inlineStr">
@@ -43892,12 +43892,12 @@
       </c>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK143" t="inlineStr">
@@ -43907,12 +43907,12 @@
       </c>
       <c r="BL143" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM143" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN143" t="inlineStr"/>
@@ -43923,27 +43923,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>663494</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -43958,21 +43958,21 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -43986,26 +43986,26 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>14.9</v>
+        <v>12.1</v>
       </c>
       <c r="Q144" t="n">
-        <v>43.2</v>
+        <v>47</v>
       </c>
       <c r="R144" t="n">
-        <v>55.1</v>
+        <v>58.7</v>
       </c>
       <c r="S144" t="n">
         <v>40.2</v>
       </c>
       <c r="T144" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U144" t="n">
-        <v>5.7</v>
+        <v>54.3</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr"/>
@@ -44061,162 +44061,162 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Contact streak: 9/25 over last 7 games</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 17.2 HR allowed</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>96.3933</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>0.109</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>0.314</t>
+        </is>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>0.111</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>42.91</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>89.56</t>
+        </is>
+      </c>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>0.3898</t>
+        </is>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>0.1537</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>27.65</t>
+        </is>
+      </c>
+      <c r="BG144" t="inlineStr">
+        <is>
+          <t>242 deg</t>
+        </is>
+      </c>
+      <c r="BH144" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BI144" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+        </is>
+      </c>
+      <c r="BJ144" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="BK144" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
-        </is>
-      </c>
-      <c r="AL144" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>28.7</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>96.2048</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>0.135</t>
-        </is>
-      </c>
-      <c r="AT144" t="inlineStr">
-        <is>
-          <t>0.293</t>
-        </is>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="AV144" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="AW144" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="BA144" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB144" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
-      </c>
-      <c r="BC144" t="inlineStr">
-        <is>
-          <t>87.1</t>
-        </is>
-      </c>
-      <c r="BD144" t="inlineStr">
-        <is>
-          <t>0.456</t>
-        </is>
-      </c>
-      <c r="BE144" t="inlineStr">
-        <is>
-          <t>0.186</t>
-        </is>
-      </c>
-      <c r="BF144" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="BG144" t="inlineStr">
-        <is>
-          <t>188 deg</t>
-        </is>
-      </c>
-      <c r="BH144" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BI144" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
-        </is>
-      </c>
-      <c r="BJ144" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="BK144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BL144" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM144" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BN144" t="inlineStr"/>
@@ -44227,27 +44227,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>663494</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -44257,17 +44257,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -44276,7 +44276,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -44294,22 +44294,22 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="Q145" t="n">
-        <v>29.4</v>
+        <v>43.2</v>
       </c>
       <c r="R145" t="n">
-        <v>45.3</v>
+        <v>55.1</v>
       </c>
       <c r="S145" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T145" t="n">
         <v>80</v>
       </c>
       <c r="U145" t="n">
-        <v>15.3</v>
+        <v>5.7</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -44348,7 +44348,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr"/>
@@ -44365,12 +44365,12 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
@@ -44380,12 +44380,12 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -44395,102 +44395,102 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>86.25</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>97.6637</t>
+          <t>96.2048</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.1069</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>188 deg</t>
         </is>
       </c>
       <c r="BH145" t="inlineStr">
@@ -44500,27 +44500,27 @@
       </c>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BK145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL145" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM145" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BN145" t="inlineStr"/>
@@ -44531,27 +44531,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -44561,26 +44561,26 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -44594,26 +44594,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>21.6</v>
+        <v>13.5</v>
       </c>
       <c r="Q146" t="n">
-        <v>42.1</v>
+        <v>29.4</v>
       </c>
       <c r="R146" t="n">
-        <v>58.7</v>
+        <v>45.3</v>
       </c>
       <c r="S146" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T146" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -44669,162 +44669,162 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Last 7 games: 4/18, 0 HR</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>34.05</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>86.25</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>97.6637</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>0.1069</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr">
+        <is>
+          <t>0.298</t>
+        </is>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>70.52</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>19.48</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>0.1285</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>40.63</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>88.79</t>
+        </is>
+      </c>
+      <c r="BD146" t="inlineStr">
+        <is>
+          <t>0.4346</t>
+        </is>
+      </c>
+      <c r="BE146" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>18.23</t>
+        </is>
+      </c>
+      <c r="BG146" t="inlineStr">
+        <is>
+          <t>286 deg</t>
+        </is>
+      </c>
+      <c r="BH146" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BI146" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+        </is>
+      </c>
+      <c r="BJ146" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="BK146" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Last 7 games: 1/20, 0 HR</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>5.83</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>35.93</t>
-        </is>
-      </c>
-      <c r="AP146" t="inlineStr">
-        <is>
-          <t>87.26</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>98.744</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>0.3376</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>0.1239</t>
-        </is>
-      </c>
-      <c r="AT146" t="inlineStr">
-        <is>
-          <t>0.2975</t>
-        </is>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>71.02</t>
-        </is>
-      </c>
-      <c r="AV146" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="AW146" t="inlineStr">
-        <is>
-          <t>39.12</t>
-        </is>
-      </c>
-      <c r="AX146" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="AZ146" t="inlineStr">
-        <is>
-          <t>0.1366</t>
-        </is>
-      </c>
-      <c r="BA146" t="inlineStr">
-        <is>
-          <t>8.55</t>
-        </is>
-      </c>
-      <c r="BB146" t="inlineStr">
-        <is>
-          <t>39.93</t>
-        </is>
-      </c>
-      <c r="BC146" t="inlineStr">
-        <is>
-          <t>90.1</t>
-        </is>
-      </c>
-      <c r="BD146" t="inlineStr">
-        <is>
-          <t>0.3721</t>
-        </is>
-      </c>
-      <c r="BE146" t="inlineStr">
-        <is>
-          <t>0.1481</t>
-        </is>
-      </c>
-      <c r="BF146" t="inlineStr">
-        <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="BG146" t="inlineStr">
-        <is>
-          <t>242 deg</t>
-        </is>
-      </c>
-      <c r="BH146" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BI146" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
-        </is>
-      </c>
-      <c r="BJ146" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="BK146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BL146" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BM146" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BN146" t="inlineStr"/>
@@ -44835,27 +44835,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -44865,26 +44865,26 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -44902,22 +44902,22 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>11.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q147" t="n">
-        <v>33.1</v>
+        <v>42.1</v>
       </c>
       <c r="R147" t="n">
-        <v>62.9</v>
+        <v>58.7</v>
       </c>
       <c r="S147" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T147" t="n">
         <v>50</v>
       </c>
       <c r="U147" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -44956,7 +44956,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -44973,12 +44973,12 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -44988,12 +44988,12 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 1/20, 0 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -45003,102 +45003,102 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>87.26</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>97.3267</t>
+          <t>98.744</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0.1239</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>242 deg</t>
         </is>
       </c>
       <c r="BH147" t="inlineStr">
@@ -45108,12 +45108,12 @@
       </c>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BK147" t="inlineStr">
@@ -45123,12 +45123,12 @@
       </c>
       <c r="BL147" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM147" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BN147" t="inlineStr"/>
@@ -45139,27 +45139,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>681146</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jonah Bride</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -45169,26 +45169,26 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -45202,26 +45202,26 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>6.7</v>
+        <v>11.8</v>
       </c>
       <c r="Q148" t="n">
-        <v>42.1</v>
+        <v>33.1</v>
       </c>
       <c r="R148" t="n">
-        <v>58.7</v>
+        <v>62.9</v>
       </c>
       <c r="S148" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T148" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U148" t="n">
-        <v>19.5</v>
+        <v>4.2</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -45260,7 +45260,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>H:2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -45272,17 +45272,17 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
@@ -45292,12 +45292,12 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Last 1 games: 1/4, 0 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -45307,57 +45307,57 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>96.7651</t>
+          <t>97.3267</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.082</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -45367,42 +45367,42 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD148" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE148" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG148" t="inlineStr">
         <is>
-          <t>242 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH148" t="inlineStr">
@@ -45412,12 +45412,12 @@
       </c>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK148" t="inlineStr">
@@ -45427,12 +45427,12 @@
       </c>
       <c r="BL148" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM148" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN148" t="inlineStr"/>
